--- a/public/exports/CONVOCATION_Apr_3_2025.xlsx
+++ b/public/exports/CONVOCATION_Apr_3_2025.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="12">
   <si>
     <t>student_number</t>
   </si>
@@ -35,7 +35,7 @@
     <t>presentation</t>
   </si>
   <si>
-    <t>19/68SE003</t>
+    <t>81/3043</t>
   </si>
   <si>
     <t>Graduated</t>
@@ -47,37 +47,10 @@
     <t>2024/2025</t>
   </si>
   <si>
-    <t>M.Ed. Educational Management</t>
+    <t>Ph.D. English</t>
   </si>
   <si>
     <t>Presentation I</t>
-  </si>
-  <si>
-    <t>16/25OE129</t>
-  </si>
-  <si>
-    <t>M.(Ed.) Educational Management</t>
-  </si>
-  <si>
-    <t>14/25OE016</t>
-  </si>
-  <si>
-    <t>14/25OE014</t>
-  </si>
-  <si>
-    <t>19/68SE004</t>
-  </si>
-  <si>
-    <t>15/25OE054</t>
-  </si>
-  <si>
-    <t>20/68OF005</t>
-  </si>
-  <si>
-    <t>14/67XC179</t>
-  </si>
-  <si>
-    <t>15/68SE013</t>
   </si>
 </sst>
 </file>
@@ -417,14 +390,14 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="17.567" bestFit="true" customWidth="true" style="0"/>
     <col min="2" max="2" width="18.71" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="22.28" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="21.138" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="36.42" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="29.421" bestFit="true" customWidth="true" style="0"/>
     <col min="6" max="6" width="17.567" bestFit="true" customWidth="true" style="0"/>
     <col min="7" max="7" width="9.10" bestFit="true" style="0"/>
   </cols>
@@ -466,166 +439,6 @@
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
         <v>11</v>
       </c>
     </row>
